--- a/Data/uncertainty/load_e.xlsx
+++ b/Data/uncertainty/load_e.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>predict_mu</t>
   </si>
   <si>
     <t>predict_min</t>
+  </si>
+  <si>
+    <t>predict_max</t>
   </si>
   <si>
     <t>mu</t>
@@ -63,7 +66,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,13 +77,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -563,142 +559,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1048,41 +1044,37 @@
   <dimension ref="A1:N97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="15.4070796460177" customWidth="1"/>
-    <col min="3" max="3" width="15.4690265486726" customWidth="1"/>
-    <col min="4" max="4" width="22.0442477876106" customWidth="1"/>
+    <col min="7" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:13">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="2"/>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2">
@@ -1095,35 +1087,35 @@
         <v>1551.33662164652</v>
       </c>
       <c r="D2">
-        <v>1552.33662164652</v>
-      </c>
-      <c r="G2" s="2">
+        <v>1602.45004502014</v>
+      </c>
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B1)-1)*4,0)</f>
         <v>1576.89333333333</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>0.969885</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <f ca="1" t="shared" ref="J2:J25" si="0">H2*I2</f>
         <v>1529.4051906</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C1)-1)*4,0)</f>
         <v>1551.33662164652</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D1)-1)*4,0)</f>
-        <v>1552.33662164652</v>
-      </c>
-      <c r="M2" s="2">
+        <v>1602.45004502014</v>
+      </c>
+      <c r="M2" s="1">
         <f ca="1" t="shared" ref="M2:M25" si="1">IF(OR(J2&gt;K2,J2&lt;L2),J2,H2)</f>
         <v>1529.4051906</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="1">
         <f ca="1" t="shared" ref="N2:N25" si="2">IF(H2=M2,0,1)</f>
         <v>1</v>
       </c>
@@ -1139,35 +1131,35 @@
         <v>1563.14457222866</v>
       </c>
       <c r="D3">
-        <v>1564.14457222866</v>
-      </c>
-      <c r="G3" s="2">
+        <v>1609.452094438</v>
+      </c>
+      <c r="G3" s="1">
         <v>1</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B2)-1)*4,0)</f>
         <v>1575.465</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>1.021257</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>1608.954659505</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C2)-1)*4,0)</f>
         <v>1548.06418630226</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D2)-1)*4,0)</f>
-        <v>1549.06418630226</v>
-      </c>
-      <c r="M3" s="2">
+        <v>1602.86581369774</v>
+      </c>
+      <c r="M3" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>1608.954659505</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1183,35 +1175,35 @@
         <v>1546.56671362677</v>
       </c>
       <c r="D4">
-        <v>1547.56671362677</v>
-      </c>
-      <c r="G4" s="2">
+        <v>1594.63661970656</v>
+      </c>
+      <c r="G4" s="1">
         <v>2</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B3)-1)*4,0)</f>
         <v>1528.61666666667</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>0.997038</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>1524.0889041</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C3)-1)*4,0)</f>
         <v>1503.72409713704</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D3)-1)*4,0)</f>
-        <v>1504.72409713704</v>
-      </c>
-      <c r="M4" s="2">
+        <v>1553.50923619629</v>
+      </c>
+      <c r="M4" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>1524.0889041</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1227,35 +1219,35 @@
         <v>1545.86985504282</v>
       </c>
       <c r="D5">
-        <v>1546.86985504282</v>
-      </c>
-      <c r="G5" s="2">
+        <v>1592.70014495718</v>
+      </c>
+      <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B4)-1)*4,0)</f>
         <v>1526.65166666667</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>1.03662</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>1582.5576507</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C4)-1)*4,0)</f>
         <v>1500.91675403036</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D4)-1)*4,0)</f>
-        <v>1501.91675403036</v>
-      </c>
-      <c r="M5" s="2">
+        <v>1552.38657930298</v>
+      </c>
+      <c r="M5" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>1582.5576507</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1271,35 +1263,35 @@
         <v>1548.06418630226</v>
       </c>
       <c r="D6">
-        <v>1549.06418630226</v>
-      </c>
-      <c r="G6" s="2">
+        <v>1602.86581369774</v>
+      </c>
+      <c r="G6" s="1">
         <v>4</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B5)-1)*4,0)</f>
         <v>1543.86666666667</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>1.034074</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>1596.47237946667</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C5)-1)*4,0)</f>
         <v>1516.93096055476</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D5)-1)*4,0)</f>
-        <v>1517.93096055476</v>
-      </c>
-      <c r="M6" s="2">
+        <v>1570.80237277858</v>
+      </c>
+      <c r="M6" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>1596.47237946667</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1315,35 +1307,35 @@
         <v>1527.35870184078</v>
       </c>
       <c r="D7">
-        <v>1528.35870184078</v>
-      </c>
-      <c r="G7" s="2">
+        <v>1575.36463149255</v>
+      </c>
+      <c r="G7" s="1">
         <v>5</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B6)-1)*4,0)</f>
         <v>1751.55833333333</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>0.988478</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>1731.37687821666</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C6)-1)*4,0)</f>
         <v>1723.84171466595</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D6)-1)*4,0)</f>
-        <v>1724.84171466595</v>
-      </c>
-      <c r="M7" s="2">
+        <v>1779.27495200072</v>
+      </c>
+      <c r="M7" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>1731.37687821666</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1359,35 +1351,35 @@
         <v>1521.77643558851</v>
       </c>
       <c r="D8">
-        <v>1522.77643558851</v>
-      </c>
-      <c r="G8" s="2">
+        <v>1563.20023107815</v>
+      </c>
+      <c r="G8" s="1">
         <v>6</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B7)-1)*4,0)</f>
         <v>1986.13666666667</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>1.00025</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>1986.63320083334</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C7)-1)*4,0)</f>
         <v>1862.90068129644</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D7)-1)*4,0)</f>
-        <v>1863.90068129644</v>
-      </c>
-      <c r="M8" s="2">
+        <v>2109.37265203689</v>
+      </c>
+      <c r="M8" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>1986.63320083334</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1403,35 +1395,35 @@
         <v>1512.69011441186</v>
       </c>
       <c r="D9">
-        <v>1513.69011441186</v>
-      </c>
-      <c r="G9" s="2">
+        <v>1554.88321892148</v>
+      </c>
+      <c r="G9" s="1">
         <v>7</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B8)-1)*4,0)</f>
         <v>2449.01</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>1.037387</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2540.57113687</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C8)-1)*4,0)</f>
         <v>2249.03286291664</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D8)-1)*4,0)</f>
-        <v>2250.03286291664</v>
-      </c>
-      <c r="M9" s="2">
+        <v>2648.98713708336</v>
+      </c>
+      <c r="M9" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2540.57113687</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1447,35 +1439,35 @@
         <v>1503.72409713704</v>
       </c>
       <c r="D10">
-        <v>1504.72409713704</v>
-      </c>
-      <c r="G10" s="2">
+        <v>1553.50923619629</v>
+      </c>
+      <c r="G10" s="1">
         <v>8</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B9)-1)*4,0)</f>
         <v>2650.49666666667</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <v>1.045036</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2769.86443454667</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C9)-1)*4,0)</f>
         <v>2356.06739831785</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D9)-1)*4,0)</f>
-        <v>2357.06739831785</v>
-      </c>
-      <c r="M10" s="2">
+        <v>2944.92593501548</v>
+      </c>
+      <c r="M10" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2769.86443454667</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1491,35 +1483,35 @@
         <v>1499.73173985565</v>
       </c>
       <c r="D11">
-        <v>1500.73173985565</v>
-      </c>
-      <c r="G11" s="2">
+        <v>1555.83159347769</v>
+      </c>
+      <c r="G11" s="1">
         <v>9</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B10)-1)*4,0)</f>
         <v>2910.68166666667</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <v>0.986436</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2871.20118054</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C10)-1)*4,0)</f>
         <v>2533.48350462286</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D10)-1)*4,0)</f>
-        <v>2534.48350462286</v>
-      </c>
-      <c r="M11" s="2">
+        <v>3287.87982871048</v>
+      </c>
+      <c r="M11" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2871.20118054</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1535,35 +1527,35 @@
         <v>1493.01445625005</v>
       </c>
       <c r="D12">
-        <v>1494.01445625005</v>
-      </c>
-      <c r="G12" s="2">
+        <v>1541.62887708328</v>
+      </c>
+      <c r="G12" s="1">
         <v>10</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B11)-1)*4,0)</f>
         <v>3089.03</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <v>0.972533</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3004.18361299</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C11)-1)*4,0)</f>
         <v>2649.54988921018</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D11)-1)*4,0)</f>
-        <v>2650.54988921018</v>
-      </c>
-      <c r="M12" s="2">
+        <v>3528.51011078982</v>
+      </c>
+      <c r="M12" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3004.18361299</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1579,35 +1571,35 @@
         <v>1483.984896533</v>
       </c>
       <c r="D13">
-        <v>1484.984896533</v>
-      </c>
-      <c r="G13" s="2">
+        <v>1547.145103467</v>
+      </c>
+      <c r="G13" s="1">
         <v>11</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B12)-1)*4,0)</f>
         <v>3130.31666666667</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>1.006938</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3152.0348037</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C12)-1)*4,0)</f>
         <v>2699.7107053896</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D12)-1)*4,0)</f>
-        <v>2700.7107053896</v>
-      </c>
-      <c r="M13" s="2">
+        <v>3560.92262794373</v>
+      </c>
+      <c r="M13" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3152.0348037</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1623,35 +1615,35 @@
         <v>1500.91675403036</v>
       </c>
       <c r="D14">
-        <v>1501.91675403036</v>
-      </c>
-      <c r="G14" s="2">
+        <v>1552.38657930298</v>
+      </c>
+      <c r="G14" s="1">
         <v>12</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B13)-1)*4,0)</f>
         <v>3208.63333333333</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="1">
         <v>1.024603</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3287.57533923333</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C13)-1)*4,0)</f>
         <v>2776.03481629133</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D13)-1)*4,0)</f>
-        <v>2777.03481629133</v>
-      </c>
-      <c r="M14" s="2">
+        <v>3641.23185037534</v>
+      </c>
+      <c r="M14" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3287.57533923333</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1667,35 +1659,35 @@
         <v>1512.87209925302</v>
       </c>
       <c r="D15">
-        <v>1513.87209925302</v>
-      </c>
-      <c r="G15" s="2">
+        <v>1565.78456741364</v>
+      </c>
+      <c r="G15" s="1">
         <v>13</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B14)-1)*4,0)</f>
         <v>3151.28166666667</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
         <v>0.985</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3104.01244166667</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C14)-1)*4,0)</f>
         <v>2713.90266654211</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D14)-1)*4,0)</f>
-        <v>2714.90266654211</v>
-      </c>
-      <c r="M15" s="2">
+        <v>3588.66066679122</v>
+      </c>
+      <c r="M15" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3104.01244166667</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1711,35 +1703,35 @@
         <v>1509.75024295317</v>
       </c>
       <c r="D16">
-        <v>1510.75024295317</v>
-      </c>
-      <c r="G16" s="2">
+        <v>1565.68642371349</v>
+      </c>
+      <c r="G16" s="1">
         <v>14</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B15)-1)*4,0)</f>
         <v>3198.86</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <v>0.989829</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3166.32439494</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C15)-1)*4,0)</f>
         <v>2746.22884113891</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D15)-1)*4,0)</f>
-        <v>2747.22884113891</v>
-      </c>
-      <c r="M16" s="2">
+        <v>3651.49115886109</v>
+      </c>
+      <c r="M16" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3166.32439494</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1755,35 +1747,35 @@
         <v>1507.2391129263</v>
       </c>
       <c r="D17">
-        <v>1508.2391129263</v>
-      </c>
-      <c r="G17" s="2">
+        <v>1558.28422040703</v>
+      </c>
+      <c r="G17" s="1">
         <v>15</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B16)-1)*4,0)</f>
         <v>3170.65666666667</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
         <v>0.997796</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3163.66853937334</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C16)-1)*4,0)</f>
         <v>2746.33402126329</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D16)-1)*4,0)</f>
-        <v>2747.33402126329</v>
-      </c>
-      <c r="M17" s="2">
+        <v>3594.97931207005</v>
+      </c>
+      <c r="M17" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3163.66853937334</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1799,35 +1791,35 @@
         <v>1516.93096055476</v>
       </c>
       <c r="D18">
-        <v>1517.93096055476</v>
-      </c>
-      <c r="G18" s="2">
+        <v>1570.80237277858</v>
+      </c>
+      <c r="G18" s="1">
         <v>16</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B17)-1)*4,0)</f>
         <v>3173.51666666667</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="1">
         <v>0.964075</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3059.50808041667</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C17)-1)*4,0)</f>
         <v>2746.08295090279</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D17)-1)*4,0)</f>
-        <v>2747.08295090279</v>
-      </c>
-      <c r="M18" s="2">
+        <v>3600.95038243055</v>
+      </c>
+      <c r="M18" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3059.50808041667</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1843,35 +1835,35 @@
         <v>1610.87129745643</v>
       </c>
       <c r="D19">
-        <v>1611.87129745643</v>
-      </c>
-      <c r="G19" s="2">
+        <v>1656.6720358769</v>
+      </c>
+      <c r="G19" s="1">
         <v>17</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B18)-1)*4,0)</f>
         <v>3131.33</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="1">
         <v>0.964811</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3021.14162863</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C18)-1)*4,0)</f>
         <v>2767.14264987693</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D18)-1)*4,0)</f>
-        <v>2768.14264987693</v>
-      </c>
-      <c r="M19" s="2">
+        <v>3495.51735012307</v>
+      </c>
+      <c r="M19" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3021.14162863</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1887,35 +1879,35 @@
         <v>1645.75983152471</v>
       </c>
       <c r="D20">
-        <v>1646.75983152471</v>
-      </c>
-      <c r="G20" s="2">
+        <v>1703.02683514196</v>
+      </c>
+      <c r="G20" s="1">
         <v>18</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B19)-1)*4,0)</f>
         <v>3041.90666666667</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="1">
         <v>1.033227</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3142.98009948</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C19)-1)*4,0)</f>
         <v>2734.83467033728</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D19)-1)*4,0)</f>
-        <v>2735.83467033728</v>
-      </c>
-      <c r="M20" s="2">
+        <v>3348.97866299605</v>
+      </c>
+      <c r="M20" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3142.98009948</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1931,35 +1923,35 @@
         <v>1660.53623369271</v>
       </c>
       <c r="D21">
-        <v>1661.53623369271</v>
-      </c>
-      <c r="G21" s="2">
+        <v>1715.34043297396</v>
+      </c>
+      <c r="G21" s="1">
         <v>19</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B20)-1)*4,0)</f>
         <v>2933.175</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="1">
         <v>1.031367</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>3025.179900225</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C20)-1)*4,0)</f>
         <v>2655.59817396274</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D20)-1)*4,0)</f>
-        <v>2656.59817396274</v>
-      </c>
-      <c r="M21" s="2">
+        <v>3210.75182603726</v>
+      </c>
+      <c r="M21" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>3025.179900225</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -1975,35 +1967,35 @@
         <v>1723.84171466595</v>
       </c>
       <c r="D22">
-        <v>1724.84171466595</v>
-      </c>
-      <c r="G22" s="2">
+        <v>1779.27495200072</v>
+      </c>
+      <c r="G22" s="1">
         <v>20</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B21)-1)*4,0)</f>
         <v>2839.995</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="1">
         <v>0.963888</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2737.43710056</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C21)-1)*4,0)</f>
         <v>2572.38247793475</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D21)-1)*4,0)</f>
-        <v>2573.38247793475</v>
-      </c>
-      <c r="M22" s="2">
+        <v>3107.60752206525</v>
+      </c>
+      <c r="M22" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2737.43710056</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2019,35 +2011,35 @@
         <v>1723.90421893968</v>
       </c>
       <c r="D23">
-        <v>1724.90421893968</v>
-      </c>
-      <c r="G23" s="2">
+        <v>1808.17911439366</v>
+      </c>
+      <c r="G23" s="1">
         <v>21</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B22)-1)*4,0)</f>
         <v>2749.45166666667</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="1">
         <v>0.956548</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2629.98249284667</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C22)-1)*4,0)</f>
         <v>2517.63645536026</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D22)-1)*4,0)</f>
-        <v>2518.63645536026</v>
-      </c>
-      <c r="M23" s="2">
+        <v>2981.26687797308</v>
+      </c>
+      <c r="M23" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2629.98249284667</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2063,35 +2055,35 @@
         <v>1749.97909531922</v>
       </c>
       <c r="D24">
-        <v>1750.97909531922</v>
-      </c>
-      <c r="G24" s="2">
+        <v>1879.55423801411</v>
+      </c>
+      <c r="G24" s="1">
         <v>22</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B23)-1)*4,0)</f>
         <v>2723.78666666667</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="1">
         <v>0.971773</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2646.90234042667</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C23)-1)*4,0)</f>
         <v>2493.18712988261</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D23)-1)*4,0)</f>
-        <v>2494.18712988261</v>
-      </c>
-      <c r="M24" s="2">
+        <v>2954.38620345072</v>
+      </c>
+      <c r="M24" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2646.90234042667</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2107,35 +2099,35 @@
         <v>1752.18413260902</v>
       </c>
       <c r="D25">
-        <v>1753.18413260902</v>
-      </c>
-      <c r="G25" s="2">
+        <v>1951.51920072431</v>
+      </c>
+      <c r="G25" s="1">
         <v>23</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <f ca="1">OFFSET($B$2,(ROW(B24)-1)*4,0)</f>
         <v>2496.55333333333</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="1">
         <v>0.975908</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <f ca="1" t="shared" si="0"/>
         <v>2436.40637042666</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" s="1">
         <f ca="1">OFFSET($C$2,(ROW(C24)-1)*4,0)</f>
         <v>2332.38190937261</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="1">
         <f ca="1">OFFSET($D$2,(ROW(D24)-1)*4,0)</f>
-        <v>2333.38190937261</v>
-      </c>
-      <c r="M25" s="2">
+        <v>2660.72475729406</v>
+      </c>
+      <c r="M25" s="1">
         <f ca="1" t="shared" si="1"/>
         <v>2436.40637042666</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="1">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2151,7 +2143,7 @@
         <v>1862.90068129644</v>
       </c>
       <c r="D26">
-        <v>1863.90068129644</v>
+        <v>2109.37265203689</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2165,7 +2157,7 @@
         <v>2243.74940953492</v>
       </c>
       <c r="D27">
-        <v>2244.74940953492</v>
+        <v>2714.73392379841</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2179,7 +2171,7 @@
         <v>2297.13681037063</v>
       </c>
       <c r="D28">
-        <v>2298.13681037063</v>
+        <v>2795.40985629604</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2193,7 +2185,7 @@
         <v>2320.97202225409</v>
       </c>
       <c r="D29">
-        <v>2321.97202225409</v>
+        <v>2794.14797774591</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2207,7 +2199,7 @@
         <v>2249.03286291664</v>
       </c>
       <c r="D30">
-        <v>2250.03286291664</v>
+        <v>2648.98713708336</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2221,7 +2213,7 @@
         <v>2166.37441626532</v>
       </c>
       <c r="D31">
-        <v>2167.37441626532</v>
+        <v>2538.97225040135</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2235,7 +2227,7 @@
         <v>2195.06968037902</v>
       </c>
       <c r="D32">
-        <v>2196.06968037902</v>
+        <v>2615.79698628765</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2249,7 +2241,7 @@
         <v>2277.69472173889</v>
       </c>
       <c r="D33">
-        <v>2278.69472173889</v>
+        <v>2785.36861159444</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2263,7 +2255,7 @@
         <v>2356.06739831785</v>
       </c>
       <c r="D34">
-        <v>2357.06739831785</v>
+        <v>2944.92593501548</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2277,7 +2269,7 @@
         <v>2418.97980294955</v>
       </c>
       <c r="D35">
-        <v>2419.97980294955</v>
+        <v>3068.97353038378</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2291,7 +2283,7 @@
         <v>2481.09079226761</v>
       </c>
       <c r="D36">
-        <v>2482.09079226761</v>
+        <v>3151.09254106573</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2305,7 +2297,7 @@
         <v>2525.08463576449</v>
       </c>
       <c r="D37">
-        <v>2526.08463576449</v>
+        <v>3220.70203090217</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2319,7 +2311,7 @@
         <v>2533.48350462286</v>
       </c>
       <c r="D38">
-        <v>2534.48350462286</v>
+        <v>3287.87982871048</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2333,7 +2325,7 @@
         <v>2585.71659776442</v>
       </c>
       <c r="D39">
-        <v>2586.71659776442</v>
+        <v>3356.60673556891</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2347,7 +2339,7 @@
         <v>2599.8168858546</v>
       </c>
       <c r="D40">
-        <v>2600.8168858546</v>
+        <v>3381.58644747873</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2361,7 +2353,7 @@
         <v>2584.85574471511</v>
       </c>
       <c r="D41">
-        <v>2585.85574471511</v>
+        <v>3391.23425528489</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2375,7 +2367,7 @@
         <v>2649.54988921018</v>
       </c>
       <c r="D42">
-        <v>2650.54988921018</v>
+        <v>3528.51011078982</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2389,7 +2381,7 @@
         <v>2665.26152048257</v>
       </c>
       <c r="D43">
-        <v>2666.26152048257</v>
+        <v>3515.67847951743</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2403,7 +2395,7 @@
         <v>2657.09999370623</v>
       </c>
       <c r="D44">
-        <v>2658.09999370623</v>
+        <v>3480.44667296044</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2417,7 +2409,7 @@
         <v>2674.58302335505</v>
       </c>
       <c r="D45">
-        <v>2675.58302335505</v>
+        <v>3488.96030997828</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2431,7 +2423,7 @@
         <v>2699.7107053896</v>
       </c>
       <c r="D46">
-        <v>2700.7107053896</v>
+        <v>3560.92262794373</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2445,7 +2437,7 @@
         <v>2741.61674644723</v>
       </c>
       <c r="D47">
-        <v>2742.61674644723</v>
+        <v>3547.15325355277</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2459,7 +2451,7 @@
         <v>2774.47373765544</v>
       </c>
       <c r="D48">
-        <v>2775.47373765544</v>
+        <v>3565.8395956779</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2473,7 +2465,7 @@
         <v>2730.2624246067</v>
       </c>
       <c r="D49">
-        <v>2731.2624246067</v>
+        <v>3561.7375753933</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2487,7 +2479,7 @@
         <v>2776.03481629133</v>
       </c>
       <c r="D50">
-        <v>2777.03481629133</v>
+        <v>3641.23185037534</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2501,7 +2493,7 @@
         <v>2782.89244901308</v>
       </c>
       <c r="D51">
-        <v>2783.89244901308</v>
+        <v>3617.62421765358</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2515,7 +2507,7 @@
         <v>2756.7179854476</v>
       </c>
       <c r="D52">
-        <v>2757.7179854476</v>
+        <v>3585.35868121906</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2529,7 +2521,7 @@
         <v>2725.98100233495</v>
       </c>
       <c r="D53">
-        <v>2726.98100233495</v>
+        <v>3565.77899766505</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2543,7 +2535,7 @@
         <v>2713.90266654211</v>
       </c>
       <c r="D54">
-        <v>2714.90266654211</v>
+        <v>3588.66066679122</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2557,7 +2549,7 @@
         <v>2703.19986261988</v>
       </c>
       <c r="D55">
-        <v>2704.19986261988</v>
+        <v>3526.86347071346</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2571,7 +2563,7 @@
         <v>2713.20803726755</v>
       </c>
       <c r="D56">
-        <v>2714.20803726755</v>
+        <v>3539.01862939912</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2585,7 +2577,7 @@
         <v>2709.13193408947</v>
       </c>
       <c r="D57">
-        <v>2710.13193408947</v>
+        <v>3554.03139924386</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2599,7 +2591,7 @@
         <v>2746.22884113891</v>
       </c>
       <c r="D58">
-        <v>2747.22884113891</v>
+        <v>3651.49115886109</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2613,7 +2605,7 @@
         <v>2748.53091404958</v>
       </c>
       <c r="D59">
-        <v>2749.53091404958</v>
+        <v>3618.37241928375</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2627,7 +2619,7 @@
         <v>2719.18309305147</v>
       </c>
       <c r="D60">
-        <v>2720.18309305147</v>
+        <v>3534.86024028186</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2641,7 +2633,7 @@
         <v>2722.99150881337</v>
       </c>
       <c r="D61">
-        <v>2723.99150881337</v>
+        <v>3538.00182451996</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2655,7 +2647,7 @@
         <v>2746.33402126329</v>
       </c>
       <c r="D62">
-        <v>2747.33402126329</v>
+        <v>3594.97931207005</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2669,7 +2661,7 @@
         <v>2727.5293591316</v>
       </c>
       <c r="D63">
-        <v>2728.5293591316</v>
+        <v>3555.65397420173</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2683,7 +2675,7 @@
         <v>2724.96319802025</v>
       </c>
       <c r="D64">
-        <v>2725.96319802025</v>
+        <v>3540.41680197975</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2697,7 +2689,7 @@
         <v>2728.19159765958</v>
       </c>
       <c r="D65">
-        <v>2729.19159765958</v>
+        <v>3537.51506900709</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2711,7 +2703,7 @@
         <v>2746.08295090279</v>
       </c>
       <c r="D66">
-        <v>2747.08295090279</v>
+        <v>3600.95038243055</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2725,7 +2717,7 @@
         <v>2714.80292335466</v>
       </c>
       <c r="D67">
-        <v>2715.80292335466</v>
+        <v>3509.28707664534</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2739,7 +2731,7 @@
         <v>2666.71511194275</v>
       </c>
       <c r="D68">
-        <v>2667.71511194275</v>
+        <v>3415.06155472392</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2753,7 +2745,7 @@
         <v>2619.6811880556</v>
       </c>
       <c r="D69">
-        <v>2620.6811880556</v>
+        <v>3334.27547861107</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2767,7 +2759,7 @@
         <v>2767.14264987693</v>
       </c>
       <c r="D70">
-        <v>2768.14264987693</v>
+        <v>3495.51735012307</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2781,7 +2773,7 @@
         <v>2805.9525489989</v>
       </c>
       <c r="D71">
-        <v>2806.9525489989</v>
+        <v>3464.63078433443</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2795,7 +2787,7 @@
         <v>2750.71619563146</v>
       </c>
       <c r="D72">
-        <v>2751.71619563146</v>
+        <v>3367.07713770188</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2809,7 +2801,7 @@
         <v>2766.62736996338</v>
       </c>
       <c r="D73">
-        <v>2767.62736996338</v>
+        <v>3374.92596336995</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2823,7 +2815,7 @@
         <v>2734.83467033728</v>
       </c>
       <c r="D74">
-        <v>2735.83467033728</v>
+        <v>3348.97866299605</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2837,7 +2829,7 @@
         <v>2714.33001556888</v>
       </c>
       <c r="D75">
-        <v>2715.33001556888</v>
+        <v>3281.08331776445</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2851,7 +2843,7 @@
         <v>2685.72881822861</v>
       </c>
       <c r="D76">
-        <v>2686.72881822861</v>
+        <v>3243.29451510472</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2865,7 +2857,7 @@
         <v>2672.37399856885</v>
       </c>
       <c r="D77">
-        <v>2673.37399856885</v>
+        <v>3210.77266809781</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2879,7 +2871,7 @@
         <v>2655.59817396274</v>
       </c>
       <c r="D78">
-        <v>2656.59817396274</v>
+        <v>3210.75182603726</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2893,7 +2885,7 @@
         <v>2620.32754745332</v>
       </c>
       <c r="D79">
-        <v>2621.32754745332</v>
+        <v>3147.62911921335</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2907,7 +2899,7 @@
         <v>2576.85127199139</v>
       </c>
       <c r="D80">
-        <v>2577.85127199139</v>
+        <v>3098.75539467527</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2921,7 +2913,7 @@
         <v>2577.61174691193</v>
       </c>
       <c r="D81">
-        <v>2578.61174691193</v>
+        <v>3114.96491975474</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2935,7 +2927,7 @@
         <v>2572.38247793475</v>
       </c>
       <c r="D82">
-        <v>2573.38247793475</v>
+        <v>3107.60752206525</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2949,7 +2941,7 @@
         <v>2578.80472953034</v>
       </c>
       <c r="D83">
-        <v>2579.80472953034</v>
+        <v>3108.25527046966</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2963,7 +2955,7 @@
         <v>2569.64831446363</v>
       </c>
       <c r="D84">
-        <v>2570.64831446363</v>
+        <v>3069.32501886971</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2977,7 +2969,7 @@
         <v>2543.12465993546</v>
       </c>
       <c r="D85">
-        <v>2544.12465993546</v>
+        <v>3029.75534006454</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2991,7 +2983,7 @@
         <v>2517.63645536026</v>
       </c>
       <c r="D86">
-        <v>2518.63645536026</v>
+        <v>2981.26687797308</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3005,7 +2997,7 @@
         <v>2522.52472752609</v>
       </c>
       <c r="D87">
-        <v>2523.52472752609</v>
+        <v>2998.52193914057</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3019,7 +3011,7 @@
         <v>2511.0630558965</v>
       </c>
       <c r="D88">
-        <v>2512.0630558965</v>
+        <v>2983.92027743684</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3033,7 +3025,7 @@
         <v>2485.54769261713</v>
       </c>
       <c r="D89">
-        <v>2486.54769261713</v>
+        <v>2958.06230738287</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3047,7 +3039,7 @@
         <v>2493.18712988261</v>
       </c>
       <c r="D90">
-        <v>2494.18712988261</v>
+        <v>2954.38620345072</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3061,7 +3053,7 @@
         <v>2438.43446349251</v>
       </c>
       <c r="D91">
-        <v>2439.43446349251</v>
+        <v>2816.27886984082</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3075,7 +3067,7 @@
         <v>2402.64264797665</v>
       </c>
       <c r="D92">
-        <v>2403.64264797665</v>
+        <v>2770.30735202335</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3089,7 +3081,7 @@
         <v>2389.40664649218</v>
       </c>
       <c r="D93">
-        <v>2390.40664649218</v>
+        <v>2737.15002017449</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3103,7 +3095,7 @@
         <v>2332.38190937261</v>
       </c>
       <c r="D94">
-        <v>2333.38190937261</v>
+        <v>2660.72475729406</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3117,7 +3109,7 @@
         <v>1764.45605896896</v>
       </c>
       <c r="D95">
-        <v>1765.45605896896</v>
+        <v>1845.0506076977</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3131,7 +3123,7 @@
         <v>1572.18797490815</v>
       </c>
       <c r="D96">
-        <v>1573.18797490815</v>
+        <v>1612.40202509184</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3145,7 +3137,7 @@
         <v>1558.07153270415</v>
       </c>
       <c r="D97">
-        <v>1559.07153270415</v>
+        <v>1596.65513396252</v>
       </c>
     </row>
   </sheetData>
